--- a/矩阵.xlsx
+++ b/矩阵.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HTC\XM2528\XM2528TEST\VL53\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0F199F-F294-4361-A84D-B4D521213DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D0512B-9365-4A04-8B3C-1BAAE9FC326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A8BF1DB1-E80F-475F-98F2-51F738224402}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>row</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -80,6 +80,18 @@
   </si>
   <si>
     <t>i*2+64+8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(i*4+j)*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(i*4+j)*2+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -462,8 +474,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE07A65-B141-46E4-8906-1067A68AE4E9}">
-  <dimension ref="A3:Q21"/>
+  <dimension ref="A3:Q39"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3">
@@ -946,7 +961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>5</v>
       </c>
@@ -957,7 +972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>0</v>
       </c>
@@ -971,7 +986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>1</v>
       </c>
@@ -983,6 +998,226 @@
       </c>
       <c r="L21" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+      <c r="J26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6</v>
+      </c>
+      <c r="H27">
+        <v>7</v>
+      </c>
+      <c r="I27" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28" s="2">
+        <v>14</v>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>17</v>
+      </c>
+      <c r="C29" s="1">
+        <v>18</v>
+      </c>
+      <c r="D29">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1">
+        <v>20</v>
+      </c>
+      <c r="F29">
+        <v>21</v>
+      </c>
+      <c r="G29" s="1">
+        <v>22</v>
+      </c>
+      <c r="H29">
+        <v>23</v>
+      </c>
+      <c r="I29" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>25</v>
+      </c>
+      <c r="C30" s="2">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>27</v>
+      </c>
+      <c r="E30" s="2">
+        <v>28</v>
+      </c>
+      <c r="F30">
+        <v>29</v>
+      </c>
+      <c r="G30" s="2">
+        <v>30</v>
+      </c>
+      <c r="H30">
+        <v>31</v>
+      </c>
+      <c r="I30" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+      <c r="J35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>6</v>
+      </c>
+      <c r="I36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
